--- a/Unit 6. Neural Models, Vision, and Foundation Models/6.1 Multi-layer Perceptron (MLP)/weights_and_biases/layer_2_weights.xlsx
+++ b/Unit 6. Neural Models, Vision, and Foundation Models/6.1 Multi-layer Perceptron (MLP)/weights_and_biases/layer_2_weights.xlsx
@@ -471,7 +471,7 @@
         <v>0.1376750077944456</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05336208276437881</v>
+        <v>0.05336208276437882</v>
       </c>
       <c r="E2" t="n">
         <v>-0.01691145379024982</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.03657278781179582</v>
+        <v>0.03657278781179581</v>
       </c>
       <c r="B6" t="n">
         <v>-0.3715751164664749</v>
@@ -654,7 +654,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.01677410160510571</v>
+        <v>-0.0167741016051057</v>
       </c>
       <c r="B8" t="n">
         <v>-0.3886780074326573</v>
@@ -686,7 +686,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.08031447970081555</v>
+        <v>0.08031447970081554</v>
       </c>
       <c r="B9" t="n">
         <v>0.0967587391389928</v>
@@ -695,13 +695,13 @@
         <v>0.2778726747190685</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09917018861958143</v>
+        <v>-0.09917018861958142</v>
       </c>
       <c r="E9" t="n">
         <v>0.2446923725540819</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.06093348880903733</v>
+        <v>-0.06093348880903734</v>
       </c>
       <c r="G9" t="n">
         <v>0.0257090157444829</v>
@@ -718,7 +718,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0477837984899676</v>
+        <v>0.04778379848996762</v>
       </c>
       <c r="B10" t="n">
         <v>-0.1333202175658474</v>
@@ -742,7 +742,7 @@
         <v>-0.280328978670672</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.04078404622086688</v>
+        <v>-0.0407840462208669</v>
       </c>
       <c r="J10" t="n">
         <v>0.5126095466331885</v>
@@ -791,7 +791,7 @@
         <v>0.2781969736945942</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03437716537130756</v>
+        <v>0.03437716537130754</v>
       </c>
       <c r="E12" t="n">
         <v>-0.3714556014819147</v>
@@ -838,7 +838,7 @@
         <v>0.1165461160860229</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03259795944503214</v>
+        <v>-0.03259795944503213</v>
       </c>
       <c r="J13" t="n">
         <v>-0.6270337557308893</v>
@@ -846,7 +846,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.03155430548873205</v>
+        <v>0.03155430548873203</v>
       </c>
       <c r="B14" t="n">
         <v>0.4203526090897836</v>
@@ -896,7 +896,7 @@
         <v>0.2962462267477134</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04983612188396906</v>
+        <v>0.04983612188396908</v>
       </c>
       <c r="H15" t="n">
         <v>0.05476732614604665</v>
@@ -916,7 +916,7 @@
         <v>-0.236333455621005</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.005183764066469572</v>
+        <v>-0.005183764066469574</v>
       </c>
       <c r="D16" t="n">
         <v>-0.4046947895886238</v>
@@ -954,13 +954,13 @@
         <v>0.1291281651164344</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.09715602226667217</v>
+        <v>-0.09715602226667218</v>
       </c>
       <c r="F17" t="n">
         <v>0.3163915142179565</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4893666213792227</v>
+        <v>0.4893666213792228</v>
       </c>
       <c r="H17" t="n">
         <v>-0.325304585499574</v>
@@ -1065,7 +1065,7 @@
         <v>0.1575976075553928</v>
       </c>
       <c r="J20" t="n">
-        <v>0.186461498472756</v>
+        <v>0.1864614984727561</v>
       </c>
     </row>
     <row r="21">
